--- a/survey_templates/025_english_proficiency_assessment--survey_templates.xlsx
+++ b/survey_templates/025_english_proficiency_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>English Proficiency Assessment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,105 +548,105 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>listening</t>
+          <t>What is your native language?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>speaking</t>
+          <t>listening_skills</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>speaking</t>
+          <t>How would you rate your listening skills?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>speaking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>What is your current level of speaking proficiency?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>Can you read and understand English texts with ease?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>grammar</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>grammar</t>
+          <t>What is your current level of writing proficiency?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,104 +658,104 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>grammar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>Can you understand and use correct English grammar?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pronunciation</t>
+          <t>vocabulary</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pronunciation</t>
+          <t>How would you rate your vocabulary?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>pronunciation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>How would you rate your pronunciation?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vocabulary_2</t>
+          <t>overall_proficiency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>How would you rate your overall English language proficiency?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reading_2</t>
+          <t>areas_of_difficulty</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>reading</t>
+          <t>Are there any areas where you struggle with the English language?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,85 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>writing_2</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>Is there anything else you would like to add about your English language proficiency?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>grammar_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>grammar</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>pronunciation_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>pronunciation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>listening_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>listening</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>native_language</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Native language</t>
         </is>
       </c>
     </row>
@@ -918,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>non-native_language</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Non-native language</t>
         </is>
       </c>
     </row>
@@ -935,301 +866,709 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>speaking_choices</t>
+          <t>listening_skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>speaking_choices</t>
+          <t>listening_skills_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>speaking_choices</t>
+          <t>listening_skills_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vocabulary_choices</t>
+          <t>listening_skills_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vocabulary_choices</t>
+          <t>listening_skills_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vocabulary_choices</t>
+          <t>speaking_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pronunciation_choices</t>
+          <t>speaking_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pronunciation_choices</t>
+          <t>speaking_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pronunciation_choices</t>
+          <t>reading_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vocabulary_2_choices</t>
+          <t>reading_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vocabulary_2_choices</t>
+          <t>reading_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vocabulary_2_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pronunciation_2_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pronunciation_2_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pronunciation_2_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>listening_2_choices</t>
+          <t>writing_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ประก_-_option1_-_option2_-_option3</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ประก - option1 - option2 - option3</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>listening_2_choices</t>
+          <t>grammar_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>grammar_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>grammar_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>somewhat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Somewhat</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vocabulary_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vocabulary_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vocabulary_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>vocabulary_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>vocabulary_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Very poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pronunciation_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>pronunciation_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pronunciation_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pronunciation_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pronunciation_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Very poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>overall_proficiency_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>overall_proficiency_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>overall_proficiency_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>overall_proficiency_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>overall_proficiency_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Very poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>areas_of_difficulty_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>speaking</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>areas_of_difficulty_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>listening</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>areas_of_difficulty_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>areas_of_difficulty_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>writing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>areas_of_difficulty_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>grammar</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>areas_of_difficulty_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>pronunciation</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pronunciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>areas_of_difficulty_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>vocabulary</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
         </is>
       </c>
     </row>
